--- a/Plantilla_StockPilot_Demo.xlsx
+++ b/Plantilla_StockPilot_Demo.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="Rd7cebbe590a14908"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="2" r:id="R6194d1a4da1a466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ventas" sheetId="3" r:id="R274e2ebe366c49f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="4" r:id="Rc476070ced1940f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveedores" sheetId="5" r:id="R2bb95f7276134bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="R1a7acdbc783c46f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="2" r:id="R46076a7deed74a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ventas" sheetId="3" r:id="R4fd46f674ec741b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="4" r:id="R88bf3770f25f4789"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveedores" sheetId="5" r:id="Racb190f9fa374d95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -515,7 +515,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>En Proveedores indique cada cuántos días visita y una fecha de próxima visita.</x:v>
+        <x:v>En Proveedores indique la última visita real y cada cuántos días visita.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1105,7 +1105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13697aeb5d97404b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafff3556399740cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15375,7 +15375,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fcc4ea8193b4a6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8fc0b271d54dc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15687,7 +15687,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R971d8931b3ba427b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f80476babc649e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15711,7 +15711,7 @@
         <x:v>frecuencia_visita_dias</x:v>
       </x:c>
       <x:c r="C1" s="8" t="str">
-        <x:v>fecha_proxima_visita</x:v>
+        <x:v>fecha_ultima_visita</x:v>
       </x:c>
       <x:c r="D1" s="8" t="str">
         <x:v>dias_entrega</x:v>
@@ -15728,7 +15728,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="34" t="n">
-        <x:v>46278</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="D2" s="28" t="n">
         <x:v>0</x:v>
@@ -15745,7 +15745,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="35" t="n">
-        <x:v>46279</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="D3" s="30" t="n">
         <x:v>0</x:v>
@@ -15762,7 +15762,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="35" t="n">
-        <x:v>46280</x:v>
+        <x:v>46277</x:v>
       </x:c>
       <x:c r="D4" s="30" t="n">
         <x:v>0</x:v>
@@ -15779,7 +15779,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="35" t="n">
-        <x:v>46281</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="D5" s="30" t="n">
         <x:v>1</x:v>
@@ -15796,7 +15796,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="35" t="n">
-        <x:v>46282</x:v>
+        <x:v>46275</x:v>
       </x:c>
       <x:c r="D6" s="30" t="n">
         <x:v>0</x:v>
@@ -15813,7 +15813,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="35" t="n">
-        <x:v>46278</x:v>
+        <x:v>46273</x:v>
       </x:c>
       <x:c r="D7" s="30" t="n">
         <x:v>0</x:v>
@@ -15830,7 +15830,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="35" t="n">
-        <x:v>46279</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="D8" s="30" t="n">
         <x:v>0</x:v>
@@ -15847,7 +15847,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="35" t="n">
-        <x:v>46280</x:v>
+        <x:v>46270</x:v>
       </x:c>
       <x:c r="D9" s="30" t="n">
         <x:v>0</x:v>
@@ -15864,7 +15864,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="35" t="n">
-        <x:v>46281</x:v>
+        <x:v>46271</x:v>
       </x:c>
       <x:c r="D10" s="30" t="n">
         <x:v>0</x:v>
@@ -15881,7 +15881,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="35" t="n">
-        <x:v>46282</x:v>
+        <x:v>46276</x:v>
       </x:c>
       <x:c r="D11" s="30" t="n">
         <x:v>0</x:v>
@@ -15898,7 +15898,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C12" s="36" t="n">
-        <x:v>46278</x:v>
+        <x:v>46271</x:v>
       </x:c>
       <x:c r="D12" s="32" t="n">
         <x:v>0</x:v>
@@ -15910,7 +15910,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09bcb038953845c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e700a8203164b41"/>
   </x:tableParts>
 </x:worksheet>
 </file>